--- a/artfynd/A 27914-2024 artfynd.xlsx
+++ b/artfynd/A 27914-2024 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>556008</v>
       </c>
       <c r="R24" t="n">
-        <v>6943607</v>
+        <v>6943608</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4444,7 +4444,7 @@
         <v>556008</v>
       </c>
       <c r="R36" t="n">
-        <v>6943607</v>
+        <v>6943608</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 27914-2024 artfynd.xlsx
+++ b/artfynd/A 27914-2024 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>556008</v>
       </c>
       <c r="R24" t="n">
-        <v>6943608</v>
+        <v>6943607</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4444,7 +4444,7 @@
         <v>556008</v>
       </c>
       <c r="R36" t="n">
-        <v>6943608</v>
+        <v>6943607</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 27914-2024 artfynd.xlsx
+++ b/artfynd/A 27914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984241</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984239</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887611</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887612</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887623</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887610</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887622</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045767</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2153,6 +2223,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984243</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887599</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2367,6 +2447,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887601</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887607</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2581,6 +2671,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887608</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887609</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2795,6 +2895,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887624</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045766</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3010,6 +3120,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984247</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,7 +3166,7 @@
         <v>556008</v>
       </c>
       <c r="R24" t="n">
-        <v>6943607</v>
+        <v>6943608</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3117,6 +3232,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887602</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3237,6 +3357,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887600</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887616</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3477,6 +3607,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887618</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3597,6 +3732,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887619</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3717,6 +3857,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887625</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3837,6 +3982,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887626</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3957,6 +4107,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887627</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4076,6 +4231,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887614</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4188,6 +4348,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887605</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4302,6 +4467,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045768</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4403,6 +4573,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95984246</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4444,7 +4619,7 @@
         <v>556008</v>
       </c>
       <c r="R36" t="n">
-        <v>6943607</v>
+        <v>6943608</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4510,6 +4685,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887603</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4617,8 +4797,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887606</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>